--- a/artfynd/A 50529-2025 artfynd.xlsx
+++ b/artfynd/A 50529-2025 artfynd.xlsx
@@ -809,7 +809,7 @@
         <v>129844844</v>
       </c>
       <c r="B3" t="n">
-        <v>105825</v>
+        <v>105829</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>129844853</v>
       </c>
       <c r="B4" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1180,7 +1180,7 @@
         <v>129844850</v>
       </c>
       <c r="B6" t="n">
-        <v>98678</v>
+        <v>98682</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1304,7 +1304,7 @@
         <v>129844851</v>
       </c>
       <c r="B7" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1556,10 +1556,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129844845</v>
+        <v>129844854</v>
       </c>
       <c r="B9" t="n">
-        <v>57736</v>
+        <v>91593</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1567,46 +1567,41 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Palleråsflon, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>494985</v>
+        <v>494834</v>
       </c>
       <c r="R9" t="n">
-        <v>7015108</v>
+        <v>7015135</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1643,7 +1638,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack, äldre på gränsen till färska, längs minst 6 meter på en granstam i äldre flerskiktad granskog. I denna skog finns flera partier med högt livsmiljövärde för tretåig hackspett baserat på volym stående död ved.</t>
+          <t>Flera fruktkroppar i stambasen av en stående död gran med full längd och potentiella födosökspår efter tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1652,12 +1647,13 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
@@ -1672,12 +1668,12 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1695,10 +1691,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129844854</v>
+        <v>129844858</v>
       </c>
       <c r="B10" t="n">
-        <v>91589</v>
+        <v>79081</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1706,30 +1702,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1737,10 +1729,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>494834</v>
+        <v>494939</v>
       </c>
       <c r="R10" t="n">
-        <v>7015135</v>
+        <v>7015094</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1775,11 +1767,6 @@
           <t>2025-11-25</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Flera fruktkroppar i stambasen av en stående död gran med full längd och potentiella födosökspår efter tretåig hackspett.</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1792,7 +1779,7 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
@@ -1807,12 +1794,12 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1830,10 +1817,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129844858</v>
+        <v>129844855</v>
       </c>
       <c r="B11" t="n">
-        <v>79081</v>
+        <v>91617</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1841,26 +1828,26 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1868,10 +1855,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>494939</v>
+        <v>494865</v>
       </c>
       <c r="R11" t="n">
-        <v>7015094</v>
+        <v>7015098</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1906,6 +1893,11 @@
           <t>2025-11-25</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Flera fruktkroppar i en levande gran.</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1918,7 +1910,7 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
@@ -1933,12 +1925,12 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1956,10 +1948,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129844855</v>
+        <v>129844857</v>
       </c>
       <c r="B12" t="n">
-        <v>91613</v>
+        <v>79081</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1967,26 +1959,26 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1994,10 +1986,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>494865</v>
+        <v>494982</v>
       </c>
       <c r="R12" t="n">
-        <v>7015098</v>
+        <v>7015109</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2034,7 +2026,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en levande gran.</t>
+          <t>På en gran med rikliga mängder ringhack av tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2049,7 +2041,7 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
@@ -2064,12 +2056,12 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2226,10 +2218,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129844857</v>
+        <v>129844847</v>
       </c>
       <c r="B14" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2237,37 +2229,46 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Palleråsflon, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>494982</v>
+        <v>494923</v>
       </c>
       <c r="R14" t="n">
-        <v>7015109</v>
+        <v>7015249</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2304,7 +2305,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>På en gran med rikliga mängder ringhack av tretåig hackspett.</t>
+          <t>Ringhack, äldre, längs ett par meter på nedre delen av en levande gran intill en rotvälta. I granskogen där fyndplatsen ligger finns partier med högt livsmiljövärde för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2313,7 +2314,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2334,12 +2334,12 @@
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2357,10 +2357,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129844847</v>
+        <v>129844862</v>
       </c>
       <c r="B15" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2368,46 +2368,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Palleråsflon, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>494923</v>
+        <v>494834</v>
       </c>
       <c r="R15" t="n">
-        <v>7015249</v>
+        <v>7015123</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2444,7 +2435,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, längs ett par meter på nedre delen av en levande gran intill en rotvälta. I granskogen där fyndplatsen ligger finns partier med högt livsmiljövärde för tretåig hackspett.</t>
+          <t>Växer på en stående delvis avbarkad död gran med potentiella födosökspår efter tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2453,6 +2444,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2473,12 +2465,12 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2496,7 +2488,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129844862</v>
+        <v>129844856</v>
       </c>
       <c r="B16" t="n">
         <v>79081</v>
@@ -2534,10 +2526,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>494834</v>
+        <v>495038</v>
       </c>
       <c r="R16" t="n">
-        <v>7015123</v>
+        <v>7015107</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2572,11 +2564,6 @@
           <t>2025-11-25</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Växer på en stående delvis avbarkad död gran med potentiella födosökspår efter tretåig hackspett.</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2589,7 +2576,7 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
@@ -2604,12 +2591,12 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2627,7 +2614,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129844856</v>
+        <v>129844863</v>
       </c>
       <c r="B17" t="n">
         <v>79081</v>
@@ -2665,10 +2652,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>495038</v>
+        <v>494865</v>
       </c>
       <c r="R17" t="n">
-        <v>7015107</v>
+        <v>7015099</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2715,7 +2702,7 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
@@ -2753,37 +2740,50 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129844863</v>
+        <v>129844852</v>
       </c>
       <c r="B18" t="n">
-        <v>79081</v>
+        <v>98778</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2791,10 +2791,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>494865</v>
+        <v>494914</v>
       </c>
       <c r="R18" t="n">
-        <v>7015099</v>
+        <v>7015130</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2829,6 +2829,11 @@
           <t>2025-11-25</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Minst 16 plantor och 1 vinterståndare inom ca 0,5 m2 yta under en gran med långväxt hänglav i äldre granskog.  Vid observationstillfället låg snö på marken, troligen finns betydligt fler plantor på och omkring fyndplatsen.</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2842,26 +2847,6 @@
       <c r="AH18" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2879,61 +2864,57 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129844852</v>
+        <v>129844845</v>
       </c>
       <c r="B19" t="n">
-        <v>98774</v>
+        <v>57736</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Palleråsflon, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>494914</v>
+        <v>494985</v>
       </c>
       <c r="R19" t="n">
-        <v>7015130</v>
+        <v>7015108</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2970,7 +2951,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Minst 16 plantor och 1 vinterståndare inom ca 0,5 m2 yta under en gran med långväxt hänglav i äldre granskog.  Vid observationstillfället låg snö på marken, troligen finns betydligt fler plantor på och omkring fyndplatsen.</t>
+          <t>Ringhack, äldre på gränsen till färska, längs minst 6 meter på en granstam i äldre flerskiktad granskog. I denna skog finns flera partier med högt livsmiljövärde för tretåig hackspett baserat på volym stående död ved.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2979,13 +2960,32 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>

--- a/artfynd/A 50529-2025 artfynd.xlsx
+++ b/artfynd/A 50529-2025 artfynd.xlsx
@@ -809,7 +809,7 @@
         <v>129844844</v>
       </c>
       <c r="B3" t="n">
-        <v>105829</v>
+        <v>105831</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>129844853</v>
       </c>
       <c r="B4" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1180,7 +1180,7 @@
         <v>129844850</v>
       </c>
       <c r="B6" t="n">
-        <v>98682</v>
+        <v>98684</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1304,7 +1304,7 @@
         <v>129844851</v>
       </c>
       <c r="B7" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1559,7 +1559,7 @@
         <v>129844854</v>
       </c>
       <c r="B9" t="n">
-        <v>91593</v>
+        <v>91595</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
         <v>129844855</v>
       </c>
       <c r="B11" t="n">
-        <v>91617</v>
+        <v>91619</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2218,10 +2218,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129844847</v>
+        <v>129844862</v>
       </c>
       <c r="B14" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2229,46 +2229,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Palleråsflon, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>494923</v>
+        <v>494834</v>
       </c>
       <c r="R14" t="n">
-        <v>7015249</v>
+        <v>7015123</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2305,7 +2296,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, längs ett par meter på nedre delen av en levande gran intill en rotvälta. I granskogen där fyndplatsen ligger finns partier med högt livsmiljövärde för tretåig hackspett.</t>
+          <t>Växer på en stående delvis avbarkad död gran med potentiella födosökspår efter tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2314,6 +2305,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2334,12 +2326,12 @@
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2357,10 +2349,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129844862</v>
+        <v>129844847</v>
       </c>
       <c r="B15" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2368,37 +2360,46 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Palleråsflon, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>494834</v>
+        <v>494923</v>
       </c>
       <c r="R15" t="n">
-        <v>7015123</v>
+        <v>7015249</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2435,7 +2436,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Växer på en stående delvis avbarkad död gran med potentiella födosökspår efter tretåig hackspett.</t>
+          <t>Ringhack, äldre, längs ett par meter på nedre delen av en levande gran intill en rotvälta. I granskogen där fyndplatsen ligger finns partier med högt livsmiljövärde för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2444,7 +2445,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2465,12 +2465,12 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2743,7 +2743,7 @@
         <v>129844852</v>
       </c>
       <c r="B18" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 50529-2025 artfynd.xlsx
+++ b/artfynd/A 50529-2025 artfynd.xlsx
@@ -1948,10 +1948,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129844857</v>
+        <v>129844846</v>
       </c>
       <c r="B12" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1959,37 +1959,46 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Palleråsflon, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>494982</v>
+        <v>494919</v>
       </c>
       <c r="R12" t="n">
-        <v>7015109</v>
+        <v>7015111</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2026,7 +2035,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>På en gran med rikliga mängder ringhack av tretåig hackspett.</t>
+          <t>Ringhack, äldre, längs minst 3 meter på en grövre granstam i äldre granskog. I denna skog finns flera partier med högt livsmiljövärde för tretåig hackspett baserat på volym stående död ved.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2035,7 +2044,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -2056,12 +2064,12 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2079,10 +2087,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129844846</v>
+        <v>129844857</v>
       </c>
       <c r="B13" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2090,46 +2098,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Palleråsflon, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>494919</v>
+        <v>494982</v>
       </c>
       <c r="R13" t="n">
-        <v>7015111</v>
+        <v>7015109</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2166,7 +2165,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, längs minst 3 meter på en grövre granstam i äldre granskog. I denna skog finns flera partier med högt livsmiljövärde för tretåig hackspett baserat på volym stående död ved.</t>
+          <t>På en gran med rikliga mängder ringhack av tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2175,6 +2174,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2195,12 +2195,12 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>

--- a/artfynd/A 50529-2025 artfynd.xlsx
+++ b/artfynd/A 50529-2025 artfynd.xlsx
@@ -1948,10 +1948,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129844846</v>
+        <v>129844857</v>
       </c>
       <c r="B12" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1959,46 +1959,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Palleråsflon, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>494919</v>
+        <v>494982</v>
       </c>
       <c r="R12" t="n">
-        <v>7015111</v>
+        <v>7015109</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2035,7 +2026,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, längs minst 3 meter på en grövre granstam i äldre granskog. I denna skog finns flera partier med högt livsmiljövärde för tretåig hackspett baserat på volym stående död ved.</t>
+          <t>På en gran med rikliga mängder ringhack av tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2044,6 +2035,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -2064,12 +2056,12 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2087,10 +2079,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129844857</v>
+        <v>129844846</v>
       </c>
       <c r="B13" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2098,37 +2090,46 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Palleråsflon, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>494982</v>
+        <v>494919</v>
       </c>
       <c r="R13" t="n">
-        <v>7015109</v>
+        <v>7015111</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2165,7 +2166,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På en gran med rikliga mängder ringhack av tretåig hackspett.</t>
+          <t>Ringhack, äldre, längs minst 3 meter på en grövre granstam i äldre granskog. I denna skog finns flera partier med högt livsmiljövärde för tretåig hackspett baserat på volym stående död ved.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2174,7 +2175,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2195,12 +2195,12 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>

--- a/artfynd/A 50529-2025 artfynd.xlsx
+++ b/artfynd/A 50529-2025 artfynd.xlsx
@@ -809,7 +809,7 @@
         <v>129844844</v>
       </c>
       <c r="B3" t="n">
-        <v>105831</v>
+        <v>105841</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -922,50 +922,37 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129844853</v>
+        <v>129844861</v>
       </c>
       <c r="B4" t="n">
-        <v>98780</v>
+        <v>79081</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -973,10 +960,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>494934</v>
+        <v>494837</v>
       </c>
       <c r="R4" t="n">
-        <v>7015145</v>
+        <v>7015163</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1013,7 +1000,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Minst 100 plantor och 8 vinterståndare inom ca 2 x 1 m2 yta i äldre granskog på frisk mark.</t>
+          <t>På gran i granskog.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1029,6 +1016,26 @@
       <c r="AH4" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1046,37 +1053,50 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129844861</v>
+        <v>129844853</v>
       </c>
       <c r="B5" t="n">
-        <v>79081</v>
+        <v>98790</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1084,10 +1104,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>494837</v>
+        <v>494934</v>
       </c>
       <c r="R5" t="n">
-        <v>7015163</v>
+        <v>7015145</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1124,7 +1144,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På gran i granskog.</t>
+          <t>Minst 100 plantor och 8 vinterståndare inom ca 2 x 1 m2 yta i äldre granskog på frisk mark.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1140,26 +1160,6 @@
       <c r="AH5" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1180,7 +1180,7 @@
         <v>129844850</v>
       </c>
       <c r="B6" t="n">
-        <v>98684</v>
+        <v>98694</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1304,7 +1304,7 @@
         <v>129844851</v>
       </c>
       <c r="B7" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1948,10 +1948,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129844846</v>
+        <v>129844857</v>
       </c>
       <c r="B12" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1959,46 +1959,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Palleråsflon, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>494919</v>
+        <v>494982</v>
       </c>
       <c r="R12" t="n">
-        <v>7015111</v>
+        <v>7015109</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2035,7 +2026,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, längs minst 3 meter på en grövre granstam i äldre granskog. I denna skog finns flera partier med högt livsmiljövärde för tretåig hackspett baserat på volym stående död ved.</t>
+          <t>På en gran med rikliga mängder ringhack av tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2044,6 +2035,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -2064,12 +2056,12 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2087,10 +2079,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129844857</v>
+        <v>129844846</v>
       </c>
       <c r="B13" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2098,37 +2090,46 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Palleråsflon, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>494982</v>
+        <v>494919</v>
       </c>
       <c r="R13" t="n">
-        <v>7015109</v>
+        <v>7015111</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2165,7 +2166,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På en gran med rikliga mängder ringhack av tretåig hackspett.</t>
+          <t>Ringhack, äldre, längs minst 3 meter på en grövre granstam i äldre granskog. I denna skog finns flera partier med högt livsmiljövärde för tretåig hackspett baserat på volym stående död ved.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2174,7 +2175,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2195,12 +2195,12 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2743,7 +2743,7 @@
         <v>129844852</v>
       </c>
       <c r="B18" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 50529-2025 artfynd.xlsx
+++ b/artfynd/A 50529-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129844859</v>
       </c>
       <c r="B2" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -809,7 +809,7 @@
         <v>129844844</v>
       </c>
       <c r="B3" t="n">
-        <v>105841</v>
+        <v>105845</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -922,37 +922,50 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129844861</v>
+        <v>129844853</v>
       </c>
       <c r="B4" t="n">
-        <v>79081</v>
+        <v>98794</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -960,10 +973,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>494837</v>
+        <v>494934</v>
       </c>
       <c r="R4" t="n">
-        <v>7015163</v>
+        <v>7015145</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1000,7 +1013,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På gran i granskog.</t>
+          <t>Minst 100 plantor och 8 vinterståndare inom ca 2 x 1 m2 yta i äldre granskog på frisk mark.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,26 +1029,6 @@
       <c r="AH4" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1053,50 +1046,37 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129844853</v>
+        <v>129844861</v>
       </c>
       <c r="B5" t="n">
-        <v>98790</v>
+        <v>79084</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1104,10 +1084,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>494934</v>
+        <v>494837</v>
       </c>
       <c r="R5" t="n">
-        <v>7015145</v>
+        <v>7015163</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1144,7 +1124,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Minst 100 plantor och 8 vinterståndare inom ca 2 x 1 m2 yta i äldre granskog på frisk mark.</t>
+          <t>På gran i granskog.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1160,6 +1140,26 @@
       <c r="AH5" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1180,7 +1180,7 @@
         <v>129844850</v>
       </c>
       <c r="B6" t="n">
-        <v>98694</v>
+        <v>98698</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1304,7 +1304,7 @@
         <v>129844851</v>
       </c>
       <c r="B7" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1428,7 +1428,7 @@
         <v>129844860</v>
       </c>
       <c r="B8" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1559,7 +1559,7 @@
         <v>129844854</v>
       </c>
       <c r="B9" t="n">
-        <v>91595</v>
+        <v>91598</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
         <v>129844858</v>
       </c>
       <c r="B10" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
         <v>129844855</v>
       </c>
       <c r="B11" t="n">
-        <v>91619</v>
+        <v>91622</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1951,7 +1951,7 @@
         <v>129844857</v>
       </c>
       <c r="B12" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2082,7 +2082,7 @@
         <v>129844846</v>
       </c>
       <c r="B13" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2221,7 +2221,7 @@
         <v>129844862</v>
       </c>
       <c r="B14" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2352,7 +2352,7 @@
         <v>129844847</v>
       </c>
       <c r="B15" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2491,7 +2491,7 @@
         <v>129844856</v>
       </c>
       <c r="B16" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2617,7 +2617,7 @@
         <v>129844863</v>
       </c>
       <c r="B17" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2743,7 +2743,7 @@
         <v>129844852</v>
       </c>
       <c r="B18" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2867,7 +2867,7 @@
         <v>129844845</v>
       </c>
       <c r="B19" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 50529-2025 artfynd.xlsx
+++ b/artfynd/A 50529-2025 artfynd.xlsx
@@ -922,50 +922,37 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129844853</v>
+        <v>129844861</v>
       </c>
       <c r="B4" t="n">
-        <v>98794</v>
+        <v>79084</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -973,10 +960,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>494934</v>
+        <v>494837</v>
       </c>
       <c r="R4" t="n">
-        <v>7015145</v>
+        <v>7015163</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1013,7 +1000,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Minst 100 plantor och 8 vinterståndare inom ca 2 x 1 m2 yta i äldre granskog på frisk mark.</t>
+          <t>På gran i granskog.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1029,6 +1016,26 @@
       <c r="AH4" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1046,37 +1053,50 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129844861</v>
+        <v>129844853</v>
       </c>
       <c r="B5" t="n">
-        <v>79084</v>
+        <v>98794</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1084,10 +1104,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>494837</v>
+        <v>494934</v>
       </c>
       <c r="R5" t="n">
-        <v>7015163</v>
+        <v>7015145</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1124,7 +1144,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På gran i granskog.</t>
+          <t>Minst 100 plantor och 8 vinterståndare inom ca 2 x 1 m2 yta i äldre granskog på frisk mark.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1140,26 +1160,6 @@
       <c r="AH5" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>

--- a/artfynd/A 50529-2025 artfynd.xlsx
+++ b/artfynd/A 50529-2025 artfynd.xlsx
@@ -1948,10 +1948,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129844857</v>
+        <v>129844846</v>
       </c>
       <c r="B12" t="n">
-        <v>79084</v>
+        <v>57737</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1959,37 +1959,46 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Palleråsflon, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>494982</v>
+        <v>494919</v>
       </c>
       <c r="R12" t="n">
-        <v>7015109</v>
+        <v>7015111</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2026,7 +2035,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>På en gran med rikliga mängder ringhack av tretåig hackspett.</t>
+          <t>Ringhack, äldre, längs minst 3 meter på en grövre granstam i äldre granskog. I denna skog finns flera partier med högt livsmiljövärde för tretåig hackspett baserat på volym stående död ved.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2035,7 +2044,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -2056,12 +2064,12 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2079,10 +2087,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129844846</v>
+        <v>129844857</v>
       </c>
       <c r="B13" t="n">
-        <v>57737</v>
+        <v>79084</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2090,46 +2098,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Palleråsflon, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>494919</v>
+        <v>494982</v>
       </c>
       <c r="R13" t="n">
-        <v>7015111</v>
+        <v>7015109</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2166,7 +2165,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, längs minst 3 meter på en grövre granstam i äldre granskog. I denna skog finns flera partier med högt livsmiljövärde för tretåig hackspett baserat på volym stående död ved.</t>
+          <t>På en gran med rikliga mängder ringhack av tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2175,6 +2174,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2195,12 +2195,12 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2218,10 +2218,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129844862</v>
+        <v>129844847</v>
       </c>
       <c r="B14" t="n">
-        <v>79084</v>
+        <v>57737</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2229,37 +2229,46 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Palleråsflon, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>494834</v>
+        <v>494923</v>
       </c>
       <c r="R14" t="n">
-        <v>7015123</v>
+        <v>7015249</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2296,7 +2305,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Växer på en stående delvis avbarkad död gran med potentiella födosökspår efter tretåig hackspett.</t>
+          <t>Ringhack, äldre, längs ett par meter på nedre delen av en levande gran intill en rotvälta. I granskogen där fyndplatsen ligger finns partier med högt livsmiljövärde för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2305,7 +2314,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2326,12 +2334,12 @@
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2349,10 +2357,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129844847</v>
+        <v>129844862</v>
       </c>
       <c r="B15" t="n">
-        <v>57737</v>
+        <v>79084</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2360,46 +2368,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Palleråsflon, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>494923</v>
+        <v>494834</v>
       </c>
       <c r="R15" t="n">
-        <v>7015249</v>
+        <v>7015123</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2436,7 +2435,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, längs ett par meter på nedre delen av en levande gran intill en rotvälta. I granskogen där fyndplatsen ligger finns partier med högt livsmiljövärde för tretåig hackspett.</t>
+          <t>Växer på en stående delvis avbarkad död gran med potentiella födosökspår efter tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2445,6 +2444,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2465,12 +2465,12 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>

--- a/artfynd/A 50529-2025 artfynd.xlsx
+++ b/artfynd/A 50529-2025 artfynd.xlsx
@@ -809,7 +809,7 @@
         <v>129844844</v>
       </c>
       <c r="B3" t="n">
-        <v>105882</v>
+        <v>105885</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -922,50 +922,37 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129844853</v>
+        <v>129844861</v>
       </c>
       <c r="B4" t="n">
-        <v>98831</v>
+        <v>79095</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -973,10 +960,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>494934</v>
+        <v>494837</v>
       </c>
       <c r="R4" t="n">
-        <v>7015145</v>
+        <v>7015163</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1013,7 +1000,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Minst 100 plantor och 8 vinterståndare inom ca 2 x 1 m2 yta i äldre granskog på frisk mark.</t>
+          <t>På gran i granskog.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1029,6 +1016,26 @@
       <c r="AH4" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1046,37 +1053,50 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129844861</v>
+        <v>129844853</v>
       </c>
       <c r="B5" t="n">
-        <v>79095</v>
+        <v>98833</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1084,10 +1104,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>494837</v>
+        <v>494934</v>
       </c>
       <c r="R5" t="n">
-        <v>7015163</v>
+        <v>7015145</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1124,7 +1144,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På gran i granskog.</t>
+          <t>Minst 100 plantor och 8 vinterståndare inom ca 2 x 1 m2 yta i äldre granskog på frisk mark.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1140,26 +1160,6 @@
       <c r="AH5" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1180,7 +1180,7 @@
         <v>129844850</v>
       </c>
       <c r="B6" t="n">
-        <v>98735</v>
+        <v>98737</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1304,7 +1304,7 @@
         <v>129844851</v>
       </c>
       <c r="B7" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1559,7 +1559,7 @@
         <v>129844854</v>
       </c>
       <c r="B9" t="n">
-        <v>91635</v>
+        <v>91637</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
         <v>129844855</v>
       </c>
       <c r="B11" t="n">
-        <v>91659</v>
+        <v>91661</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2218,10 +2218,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129844847</v>
+        <v>129844862</v>
       </c>
       <c r="B14" t="n">
-        <v>57741</v>
+        <v>79095</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2229,46 +2229,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Palleråsflon, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>494923</v>
+        <v>494834</v>
       </c>
       <c r="R14" t="n">
-        <v>7015249</v>
+        <v>7015123</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2305,7 +2296,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, längs ett par meter på nedre delen av en levande gran intill en rotvälta. I granskogen där fyndplatsen ligger finns partier med högt livsmiljövärde för tretåig hackspett.</t>
+          <t>Växer på en stående delvis avbarkad död gran med potentiella födosökspår efter tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2314,6 +2305,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2334,12 +2326,12 @@
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2357,10 +2349,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129844862</v>
+        <v>129844847</v>
       </c>
       <c r="B15" t="n">
-        <v>79095</v>
+        <v>57741</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2368,37 +2360,46 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Palleråsflon, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>494834</v>
+        <v>494923</v>
       </c>
       <c r="R15" t="n">
-        <v>7015123</v>
+        <v>7015249</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2435,7 +2436,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Växer på en stående delvis avbarkad död gran med potentiella födosökspår efter tretåig hackspett.</t>
+          <t>Ringhack, äldre, längs ett par meter på nedre delen av en levande gran intill en rotvälta. I granskogen där fyndplatsen ligger finns partier med högt livsmiljövärde för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2444,7 +2445,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2465,12 +2465,12 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2743,7 +2743,7 @@
         <v>129844852</v>
       </c>
       <c r="B18" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 50529-2025 artfynd.xlsx
+++ b/artfynd/A 50529-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129844859</v>
       </c>
       <c r="B2" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -809,7 +809,7 @@
         <v>129844844</v>
       </c>
       <c r="B3" t="n">
-        <v>105885</v>
+        <v>105972</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -922,37 +922,50 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129844861</v>
+        <v>129844853</v>
       </c>
       <c r="B4" t="n">
-        <v>79095</v>
+        <v>98920</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -960,10 +973,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>494837</v>
+        <v>494934</v>
       </c>
       <c r="R4" t="n">
-        <v>7015163</v>
+        <v>7015145</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1000,7 +1013,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På gran i granskog.</t>
+          <t>Minst 100 plantor och 8 vinterståndare inom ca 2 x 1 m2 yta i äldre granskog på frisk mark.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,26 +1029,6 @@
       <c r="AH4" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1053,50 +1046,37 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129844853</v>
+        <v>129844861</v>
       </c>
       <c r="B5" t="n">
-        <v>98833</v>
+        <v>79180</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1104,10 +1084,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>494934</v>
+        <v>494837</v>
       </c>
       <c r="R5" t="n">
-        <v>7015145</v>
+        <v>7015163</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1144,7 +1124,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Minst 100 plantor och 8 vinterståndare inom ca 2 x 1 m2 yta i äldre granskog på frisk mark.</t>
+          <t>På gran i granskog.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1160,6 +1140,26 @@
       <c r="AH5" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1180,7 +1180,7 @@
         <v>129844850</v>
       </c>
       <c r="B6" t="n">
-        <v>98737</v>
+        <v>98824</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1304,7 +1304,7 @@
         <v>129844851</v>
       </c>
       <c r="B7" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1428,7 +1428,7 @@
         <v>129844860</v>
       </c>
       <c r="B8" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1559,7 +1559,7 @@
         <v>129844854</v>
       </c>
       <c r="B9" t="n">
-        <v>91637</v>
+        <v>91724</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
         <v>129844858</v>
       </c>
       <c r="B10" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
         <v>129844855</v>
       </c>
       <c r="B11" t="n">
-        <v>91661</v>
+        <v>91748</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1951,7 +1951,7 @@
         <v>129844857</v>
       </c>
       <c r="B12" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2082,7 +2082,7 @@
         <v>129844846</v>
       </c>
       <c r="B13" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2221,7 +2221,7 @@
         <v>129844862</v>
       </c>
       <c r="B14" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2352,7 +2352,7 @@
         <v>129844847</v>
       </c>
       <c r="B15" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2491,7 +2491,7 @@
         <v>129844856</v>
       </c>
       <c r="B16" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2617,7 +2617,7 @@
         <v>129844863</v>
       </c>
       <c r="B17" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2743,7 +2743,7 @@
         <v>129844852</v>
       </c>
       <c r="B18" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2867,7 +2867,7 @@
         <v>129844845</v>
       </c>
       <c r="B19" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 50529-2025 artfynd.xlsx
+++ b/artfynd/A 50529-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129844859</v>
       </c>
       <c r="B2" t="n">
-        <v>79180</v>
+        <v>79095</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -809,7 +809,7 @@
         <v>129844844</v>
       </c>
       <c r="B3" t="n">
-        <v>105972</v>
+        <v>105885</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -922,50 +922,37 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129844853</v>
+        <v>129844861</v>
       </c>
       <c r="B4" t="n">
-        <v>98920</v>
+        <v>79095</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -973,10 +960,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>494934</v>
+        <v>494837</v>
       </c>
       <c r="R4" t="n">
-        <v>7015145</v>
+        <v>7015163</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1013,7 +1000,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Minst 100 plantor och 8 vinterståndare inom ca 2 x 1 m2 yta i äldre granskog på frisk mark.</t>
+          <t>På gran i granskog.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1029,6 +1016,26 @@
       <c r="AH4" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1046,37 +1053,50 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129844861</v>
+        <v>129844853</v>
       </c>
       <c r="B5" t="n">
-        <v>79180</v>
+        <v>98833</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1084,10 +1104,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>494837</v>
+        <v>494934</v>
       </c>
       <c r="R5" t="n">
-        <v>7015163</v>
+        <v>7015145</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1124,7 +1144,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På gran i granskog.</t>
+          <t>Minst 100 plantor och 8 vinterståndare inom ca 2 x 1 m2 yta i äldre granskog på frisk mark.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1140,26 +1160,6 @@
       <c r="AH5" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1180,7 +1180,7 @@
         <v>129844850</v>
       </c>
       <c r="B6" t="n">
-        <v>98824</v>
+        <v>98737</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1304,7 +1304,7 @@
         <v>129844851</v>
       </c>
       <c r="B7" t="n">
-        <v>98920</v>
+        <v>98833</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1428,7 +1428,7 @@
         <v>129844860</v>
       </c>
       <c r="B8" t="n">
-        <v>79180</v>
+        <v>79095</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1559,7 +1559,7 @@
         <v>129844854</v>
       </c>
       <c r="B9" t="n">
-        <v>91724</v>
+        <v>91637</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
         <v>129844858</v>
       </c>
       <c r="B10" t="n">
-        <v>79180</v>
+        <v>79095</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
         <v>129844855</v>
       </c>
       <c r="B11" t="n">
-        <v>91748</v>
+        <v>91661</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1951,7 +1951,7 @@
         <v>129844857</v>
       </c>
       <c r="B12" t="n">
-        <v>79180</v>
+        <v>79095</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2082,7 +2082,7 @@
         <v>129844846</v>
       </c>
       <c r="B13" t="n">
-        <v>57826</v>
+        <v>57741</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2221,7 +2221,7 @@
         <v>129844862</v>
       </c>
       <c r="B14" t="n">
-        <v>79180</v>
+        <v>79095</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2352,7 +2352,7 @@
         <v>129844847</v>
       </c>
       <c r="B15" t="n">
-        <v>57826</v>
+        <v>57741</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2491,7 +2491,7 @@
         <v>129844856</v>
       </c>
       <c r="B16" t="n">
-        <v>79180</v>
+        <v>79095</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2617,7 +2617,7 @@
         <v>129844863</v>
       </c>
       <c r="B17" t="n">
-        <v>79180</v>
+        <v>79095</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2743,7 +2743,7 @@
         <v>129844852</v>
       </c>
       <c r="B18" t="n">
-        <v>98920</v>
+        <v>98833</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2867,7 +2867,7 @@
         <v>129844845</v>
       </c>
       <c r="B19" t="n">
-        <v>57826</v>
+        <v>57741</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 50529-2025 artfynd.xlsx
+++ b/artfynd/A 50529-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AY18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129844859</v>
+        <v>129844854</v>
       </c>
       <c r="B2" t="n">
-        <v>79095</v>
+        <v>91905</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,26 +686,30 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -713,10 +717,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>494950</v>
+        <v>494834</v>
       </c>
       <c r="R2" t="n">
-        <v>7015161</v>
+        <v>7015135</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -753,7 +757,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Enstaka på gran.</t>
+          <t>Flera fruktkroppar i stambasen av en stående död gran med full längd och potentiella födosökspår efter tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -783,12 +787,12 @@
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -806,42 +810,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129844844</v>
+        <v>129844856</v>
       </c>
       <c r="B3" t="n">
-        <v>105885</v>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221725</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -849,10 +848,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>494967</v>
+        <v>495038</v>
       </c>
       <c r="R3" t="n">
-        <v>7015276</v>
+        <v>7015107</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,11 +886,6 @@
           <t>2025-11-25</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Vintergröna blad och fröställningar i barrblandskog.</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -905,6 +899,26 @@
       <c r="AH3" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -922,14 +936,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129844861</v>
+        <v>129844857</v>
       </c>
       <c r="B4" t="n">
-        <v>79095</v>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -960,10 +974,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>494837</v>
+        <v>494982</v>
       </c>
       <c r="R4" t="n">
-        <v>7015163</v>
+        <v>7015109</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1000,7 +1014,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På gran i granskog.</t>
+          <t>På en gran med rikliga mängder ringhack av tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1053,10 +1067,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129844853</v>
+        <v>129844858</v>
       </c>
       <c r="B5" t="n">
-        <v>98833</v>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1064,39 +1078,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1104,10 +1105,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>494934</v>
+        <v>494939</v>
       </c>
       <c r="R5" t="n">
-        <v>7015145</v>
+        <v>7015094</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1142,11 +1143,6 @@
           <t>2025-11-25</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Minst 100 plantor och 8 vinterståndare inom ca 2 x 1 m2 yta i äldre granskog på frisk mark.</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1160,6 +1156,26 @@
       <c r="AH5" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1177,50 +1193,37 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129844850</v>
+        <v>129844859</v>
       </c>
       <c r="B6" t="n">
-        <v>98737</v>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220093</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Châtel.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1228,10 +1231,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>494930</v>
+        <v>494950</v>
       </c>
       <c r="R6" t="n">
-        <v>7015286</v>
+        <v>7015161</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1268,7 +1271,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>1 vinterståndare i barrskog på fuktig mark.</t>
+          <t>Enstaka på gran.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1283,7 +1286,27 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>Barrsumpskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1301,10 +1324,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129844851</v>
+        <v>129844860</v>
       </c>
       <c r="B7" t="n">
-        <v>98833</v>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1312,39 +1335,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1352,10 +1362,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>494952</v>
+        <v>494888</v>
       </c>
       <c r="R7" t="n">
-        <v>7015131</v>
+        <v>7015192</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1392,7 +1402,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Minst 15 plantor och 4 vinterståndare inom ca 0,5 m2 yta i äldre granskog. Vid observationstillfället låg snö på marken, troligen finns betydligt fler plantor på fyndplatsen.</t>
+          <t>Växer på döda grenar av en grov gammal gran i äldre granskog.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1408,6 +1418,26 @@
       <c r="AH7" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1425,14 +1455,14 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129844860</v>
+        <v>129844861</v>
       </c>
       <c r="B8" t="n">
-        <v>79095</v>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1463,10 +1493,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>494888</v>
+        <v>494837</v>
       </c>
       <c r="R8" t="n">
-        <v>7015192</v>
+        <v>7015163</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1503,7 +1533,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Växer på döda grenar av en grov gammal gran i äldre granskog.</t>
+          <t>På gran i granskog.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1556,41 +1586,37 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129844854</v>
+        <v>129844862</v>
       </c>
       <c r="B9" t="n">
-        <v>91637</v>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1601,7 +1627,7 @@
         <v>494834</v>
       </c>
       <c r="R9" t="n">
-        <v>7015135</v>
+        <v>7015123</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1638,7 +1664,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i stambasen av en stående död gran med full längd och potentiella födosökspår efter tretåig hackspett.</t>
+          <t>Växer på en stående delvis avbarkad död gran med potentiella födosökspår efter tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1653,7 +1679,7 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
@@ -1691,14 +1717,14 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129844858</v>
+        <v>129844863</v>
       </c>
       <c r="B10" t="n">
-        <v>79095</v>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1729,10 +1755,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>494939</v>
+        <v>494865</v>
       </c>
       <c r="R10" t="n">
-        <v>7015094</v>
+        <v>7015099</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1817,10 +1843,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129844855</v>
+        <v>129844845</v>
       </c>
       <c r="B11" t="n">
-        <v>91661</v>
+        <v>57953</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1828,37 +1854,46 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Palleråsflon, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>494865</v>
+        <v>494985</v>
       </c>
       <c r="R11" t="n">
-        <v>7015098</v>
+        <v>7015108</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1895,7 +1930,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en levande gran.</t>
+          <t>Ringhack, äldre på gränsen till färska, längs minst 6 meter på en granstam i äldre flerskiktad granskog. I denna skog finns flera partier med högt livsmiljövärde för tretåig hackspett baserat på volym stående död ved.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1904,13 +1939,12 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
@@ -1948,10 +1982,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129844857</v>
+        <v>129844846</v>
       </c>
       <c r="B12" t="n">
-        <v>79095</v>
+        <v>57953</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1959,37 +1993,46 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Palleråsflon, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>494982</v>
+        <v>494919</v>
       </c>
       <c r="R12" t="n">
-        <v>7015109</v>
+        <v>7015111</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2026,7 +2069,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>På en gran med rikliga mängder ringhack av tretåig hackspett.</t>
+          <t>Ringhack, äldre, längs minst 3 meter på en grövre granstam i äldre granskog. I denna skog finns flera partier med högt livsmiljövärde för tretåig hackspett baserat på volym stående död ved.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2035,7 +2078,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -2056,12 +2098,12 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2079,10 +2121,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129844846</v>
+        <v>129844847</v>
       </c>
       <c r="B13" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2126,10 +2168,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>494919</v>
+        <v>494923</v>
       </c>
       <c r="R13" t="n">
-        <v>7015111</v>
+        <v>7015249</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2166,7 +2208,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, längs minst 3 meter på en grövre granstam i äldre granskog. I denna skog finns flera partier med högt livsmiljövärde för tretåig hackspett baserat på volym stående död ved.</t>
+          <t>Ringhack, äldre, längs ett par meter på nedre delen av en levande gran intill en rotvälta. I granskogen där fyndplatsen ligger finns partier med högt livsmiljövärde för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2218,37 +2260,50 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129844862</v>
+        <v>129844850</v>
       </c>
       <c r="B14" t="n">
-        <v>79095</v>
+        <v>99022</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>220093</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2256,10 +2311,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>494834</v>
+        <v>494930</v>
       </c>
       <c r="R14" t="n">
-        <v>7015123</v>
+        <v>7015286</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2296,7 +2351,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Växer på en stående delvis avbarkad död gran med potentiella födosökspår efter tretåig hackspett.</t>
+          <t>1 vinterståndare i barrskog på fuktig mark.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2311,27 +2366,7 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Barrsumpskog</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2349,57 +2384,61 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129844847</v>
+        <v>129844851</v>
       </c>
       <c r="B15" t="n">
-        <v>57741</v>
+        <v>99118</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Palleråsflon, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>494923</v>
+        <v>494952</v>
       </c>
       <c r="R15" t="n">
-        <v>7015249</v>
+        <v>7015131</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2436,7 +2475,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, längs ett par meter på nedre delen av en levande gran intill en rotvälta. I granskogen där fyndplatsen ligger finns partier med högt livsmiljövärde för tretåig hackspett.</t>
+          <t>Minst 15 plantor och 4 vinterståndare inom ca 0,5 m2 yta i äldre granskog. Vid observationstillfället låg snö på marken, troligen finns betydligt fler plantor på fyndplatsen.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2445,32 +2484,13 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2488,37 +2508,50 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129844856</v>
+        <v>129844852</v>
       </c>
       <c r="B16" t="n">
-        <v>79095</v>
+        <v>99118</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2526,10 +2559,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>495038</v>
+        <v>494914</v>
       </c>
       <c r="R16" t="n">
-        <v>7015107</v>
+        <v>7015130</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2564,6 +2597,11 @@
           <t>2025-11-25</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Minst 16 plantor och 1 vinterståndare inom ca 0,5 m2 yta under en gran med långväxt hänglav i äldre granskog.  Vid observationstillfället låg snö på marken, troligen finns betydligt fler plantor på och omkring fyndplatsen.</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2576,27 +2614,7 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2614,37 +2632,50 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129844863</v>
+        <v>129844853</v>
       </c>
       <c r="B17" t="n">
-        <v>79095</v>
+        <v>99118</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2652,10 +2683,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>494865</v>
+        <v>494934</v>
       </c>
       <c r="R17" t="n">
-        <v>7015099</v>
+        <v>7015145</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2690,6 +2721,11 @@
           <t>2025-11-25</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Minst 100 plantor och 8 vinterståndare inom ca 2 x 1 m2 yta i äldre granskog på frisk mark.</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2703,26 +2739,6 @@
       <c r="AH17" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2740,44 +2756,36 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129844852</v>
+        <v>129844844</v>
       </c>
       <c r="B18" t="n">
-        <v>98833</v>
+        <v>106228</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>221725</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -2791,10 +2799,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>494914</v>
+        <v>494967</v>
       </c>
       <c r="R18" t="n">
-        <v>7015130</v>
+        <v>7015276</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2831,7 +2839,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Minst 16 plantor och 1 vinterståndare inom ca 0,5 m2 yta under en gran med långväxt hänglav i äldre granskog.  Vid observationstillfället låg snö på marken, troligen finns betydligt fler plantor på och omkring fyndplatsen.</t>
+          <t>Vintergröna blad och fröställningar i barrblandskog.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2846,7 +2854,7 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2861,145 +2869,6 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>129844845</v>
-      </c>
-      <c r="B19" t="n">
-        <v>57741</v>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>Palleråsflon, Jmt</t>
-        </is>
-      </c>
-      <c r="Q19" t="n">
-        <v>494985</v>
-      </c>
-      <c r="R19" t="n">
-        <v>7015108</v>
-      </c>
-      <c r="S19" t="n">
-        <v>10</v>
-      </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V19" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>Lit</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>2025-11-25</t>
-        </is>
-      </c>
-      <c r="AA19" t="inlineStr">
-        <is>
-          <t>2025-11-25</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre på gränsen till färska, längs minst 6 meter på en granstam i äldre flerskiktad granskog. I denna skog finns flera partier med högt livsmiljövärde för tretåig hackspett baserat på volym stående död ved.</t>
-        </is>
-      </c>
-      <c r="AD19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
-      </c>
-      <c r="AT19" t="inlineStr"/>
-      <c r="AW19" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 50529-2025 artfynd.xlsx
+++ b/artfynd/A 50529-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AZ18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -807,6 +812,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129844854</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -933,6 +943,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129844856</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1064,6 +1079,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129844857</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1190,6 +1210,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129844858</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1321,6 +1346,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129844859</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1452,6 +1482,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129844860</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1583,6 +1618,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129844861</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1714,6 +1754,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129844862</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1840,6 +1885,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129844863</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1979,6 +2029,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129844845</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2118,6 +2173,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129844846</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2257,6 +2317,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129844847</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2381,6 +2446,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129844850</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2505,6 +2575,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129844851</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2629,6 +2704,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129844852</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2753,6 +2833,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129844853</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2869,8 +2954,32 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129844844</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>